--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:16</t>
+    <t xml:space="preserve">2026-09-09 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:11</t>
+    <t xml:space="preserve">2026-09-17 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:07</t>
+    <t xml:space="preserve">2026-09-23 12:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:36</t>
+    <t xml:space="preserve">2026-10-02 14:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:38</t>
+    <t xml:space="preserve">2026-10-05 10:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -874,7 +874,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>229643.12</v>
+        <v>229643.13</v>
       </c>
     </row>
     <row r="21">
